--- a/src/test/resources/ImportTemplate/Recon - Redshift.xlsx
+++ b/src/test/resources/ImportTemplate/Recon - Redshift.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AF8CFC-E519-43C5-88B4-F93D2F70DFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8908480E-DA4D-420E-B8C4-8A6458A68324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <t>Select * from icedqrs.regression_database.staff</t>
   </si>
   <si>
-    <t>Recon--ImportSQL--Redshift--Staff_table</t>
+    <t>Recon_ImportSQL--CDW-Redshift_Staff</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Recon - Redshift.xlsx
+++ b/src/test/resources/ImportTemplate/Recon - Redshift.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8908480E-DA4D-420E-B8C4-8A6458A68324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C3FC8D-B660-49DE-B1E8-F5698A4AD7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
     <t>Select * from icedqrs.regression_database.staff</t>
   </si>
   <si>
-    <t>Recon_ImportSQL--CDW-Redshift_Staff</t>
+    <t>Recon_ImportSQL__CDW_Redshift_Staff</t>
   </si>
 </sst>
 </file>
